--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_valparaiso_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_valparaiso_provincial.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:08</t>
+    <t xml:space="preserve">2026-09-29 14:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_valparaiso_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_valparaiso_provincial.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:02</t>
+    <t xml:space="preserve">2026-09-29 18:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -519,7 +519,7 @@
         <v>5.77</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>37.68</v>
+        <v>37.67</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>31.91</v>
@@ -547,10 +547,10 @@
         <v>2.18</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>41.21</v>
+        <v>41.22</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>39.04</v>
+        <v>39.03</v>
       </c>
     </row>
     <row r="6">
@@ -561,10 +561,10 @@
         <v>1.47</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>32.79</v>
+        <v>32.8</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>31.32</v>
+        <v>31.33</v>
       </c>
     </row>
     <row r="7">

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_valparaiso_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_valparaiso_provincial.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:36</t>
+    <t xml:space="preserve">2026-10-05 04:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -519,7 +519,7 @@
         <v>5.77</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>37.67</v>
+        <v>37.68</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>31.91</v>
@@ -550,7 +550,7 @@
         <v>41.22</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>39.03</v>
+        <v>39.04</v>
       </c>
     </row>
     <row r="6">
